--- a/Extracted_data_analysis/polar/Output-Transformed_data/summary_counts_question_4.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/summary_counts_question_4.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">meso_design</t>
   </si>
@@ -27,6 +27,9 @@
     <t xml:space="preserve">Percentage</t>
   </si>
   <si>
+    <t xml:space="preserve">depth(transect(quadrat))</t>
+  </si>
+  <si>
     <t xml:space="preserve">nd</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
   </si>
   <si>
     <t xml:space="preserve">sediment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slope+temperature</t>
   </si>
   <si>
     <t xml:space="preserve">temperature</t>
@@ -465,10 +471,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +482,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -490,7 +496,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6">
@@ -509,10 +515,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -520,10 +526,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +540,7 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="9">
@@ -542,10 +548,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>10.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="10">
@@ -553,10 +559,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -564,10 +570,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>27.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="12">
@@ -575,10 +581,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="13">
@@ -589,7 +595,18 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -605,7 +622,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -616,24 +633,24 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>96.6</v>
+        <v>96.7</v>
       </c>
     </row>
   </sheetData>
@@ -649,7 +666,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -660,24 +677,24 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>79.3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>20.7</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +710,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -704,46 +721,46 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -759,7 +776,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -770,134 +787,145 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
